--- a/data/daily/2026-10/2026-10-11.xlsx
+++ b/data/daily/2026-10/2026-10-11.xlsx
@@ -1170,7 +1170,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="457200" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1342,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1367,35 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,7 +1425,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1450,27 +1450,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,49 +1503,49 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,24 +1553,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1553,24 +1578,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1578,79 +1603,54 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,33 +2596,29 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16251</v>
+        <v>16252</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 복용 후 피곤함이 덜 느껴지고 활력에 도움이 됨</t>
+          <t>피로 회복 체감 — 섭취 후 피로감이 덜해지고 활력 충전에 도움 됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 포장 구성 — 구성 및 디자인이 깔끔하고 고급스러워 선물용으로 적합함</t>
+          <t>선물용 패키지 만족 — 포장이 깔끔하고 튼튼하며 디자인이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>간편한 섭취 방식 — 맛이 좋고 간편하게 챙겨 먹기 편리함</t>
+          <t>간편한 섭취 — 액상과 정제 구성으로 어디서나 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송이 매우 느려 받기까지 오랜 시간이 걸림</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>압도적 우위 부족 — 가격 대비 타 건강기능식품 대비 확실한 차별성은 애매함</t>
-        </is>
-      </c>
+          <t>대체재 대비 특장점 모호 — 시중 건강기능식품 선택지가 다양해 압도적인 차별성이 부족하다는 의견 있음</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -2667,22 +2663,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>기력 충전 도움 — 피곤하거나 지칠 때 먹으면 기운을 차리는 데 효과적임</t>
+          <t>피로 시 간편한 활력 충전 — 지치거나 피곤할 때 하나씩 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 배송 포장이 예쁘게 와서 주는 사람과 받는 사람 모두 만족함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>편리한 복용 — 환절기 건강 관리 및 피로 시 챙겨 마시기 편함</t>
-        </is>
-      </c>
+          <t>선물용 디자인 만족 — 패키지가 깔끔하고 예뻐 선물용 및 수령용 모두 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>심각한 배송 지연 — 배송이 매우 늦어져 구매 과정에서 불편함을 겪음</t>
+          <t>배송 지연 불만 — 배송이 심하게 지연되어 수령 시 불편을 겪었다는 의견 있음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2730,17 +2722,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 — 복용 시 몸의 활력이 달라지고 다음 날 피로가 확실히 줄어듦</t>
+          <t>뚜렷한 피로 회복 체감 — 복용 후 다음 날 피로가 덜하고 몸에 활력이 생기는 체감 효과가 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>꼼꼼한 배송 포장 — 포장이 꼼꼼하게 되어 배송 상태가 양호함</t>
+          <t>진한 액상 맛과 퀄리티 — 타 액상 비타민 대비 맛이 진하고 고품질로 느껴짐</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>우수한 액상 농도 — 타 액상 비타민 대비 액상이 진하고 품질이 뛰어남</t>
+          <t>꼼꼼한 선물 포장 — 포장이 정성스럽고 꼼꼼하여 선물로 주고받기 좋음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2789,17 +2781,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 새콤달콤한 젤리 형태로 간식처럼 맛있게 섭취 가능함</t>
+          <t>맛있는 구미 형태 — 새콤달콤한 젤리 형태로 간식처럼 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>쉬운 영양제 섭취 — 알약을 잘 못 먹는 사람도 부담 없이 챙겨 먹기 편함</t>
+          <t>편리한 복용 편의성 — 알약을 잘 삼키지 못하는 사람도 부담 없이 영양을 챙길 수 있음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>귀여운 패키지 디자인 — 패키지 형태와 증정품 키캡 디자인이 귀여움</t>
+          <t>귀여운 선물 패키지 — 손잡이가 달린 귀여운 디자인과 꼼꼼한 포장으로 선물 만족도가 높음</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2848,22 +2840,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 며칠만 복용해도 오후 시간대 체력 저하와 피로감이 줄어듦</t>
+          <t>빠른 피로 개선 체감 — 섭취 후 오후 피로감이나 체력 저하가 줄어들고 에너지 충전에 도움 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성 — 개별 포장이 견고하여 출근이나 여행 시 가방에 넣기 편리함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 물 없이도 간편하게 먹을 수 있고 목넘김이 양호함</t>
-        </is>
-      </c>
+          <t>간편한 휴대 및 섭취 — 물 없이도 개별 포장 병 형태로 출근길이나 야외에서 간편 복용 가능함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>아쉬운 배송 포장 — 선물용 쇼핑백이나 포장 신경 씀 없이 박스에 그대로 배송됨</t>
+          <t>배송 포장 아쉬움 — 쇼핑백 미동봉 및 일반 박스 배송으로 선물용 포장에 아쉬움이 있음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2907,26 +2895,26 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8747</v>
+        <v>8748</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>편리한 개별 휴대 — 소포장 한 포씩 외출 시 가방에 넣어 다니며 챙기기 좋음</t>
+          <t>간편한 일체형 복용 — 알약과 음료가 세트로 구성되어 휴대 및 섭취가 간편함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>아침 피로 감소 — 자기 전 복용 시 아침 피로 회복에 도움이 됨</t>
+          <t>아침 피로 완화 — 취침 전이나 피곤할 때 섭취 시 다음 날 아침 컨디션 회복에 도움 됨</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>고급스러운 구성 — 알약과 음료 세트 구성으로 고급스러운 느낌을 줌</t>
+          <t>고급스러운 포장 — 포장이 깔끔하고 고급스러워 가벼운 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>풍성함 부족한 부피 — 소포장이라 풍성해 보이는 선물 느낌은 약간 부족함</t>
+          <t>다소 작은 소포장 볼륨 — 소포장 구성이라 선물로서 풍성해 보이지 않을 수 있음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2974,17 +2962,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 박스와 종이가방 포장이 예쁘고 고급스러워 명절 선물에 적합함</t>
+          <t>고급스러운 명절 패키지 — 전용 박스와 종이가방 구성이 고급스러워 명절 선물로 적합함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>출근 시 간편 섭취 — 한 병씩 개별 구성되어 있어 출근할 때 챙겨 먹기 편리함</t>
+          <t>출근 시 간편한 복용 — 1병 단위 개별 포장이라 출근길에 챙겨 먹기 수월함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>면역 및 활력 유지 — 체력이 떨어지는 시기나 환절기에 면역력 유지에 도움됨</t>
+          <t>활력 충전 효과 — 바쁜 일상이나 환절기 면역 및 체력 보충에 도움 됨</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3033,17 +3021,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성과 여성을 위한 맞춤 비타민으로 구분되어 선물용으로 좋음</t>
+          <t>성별 맞춤형 설계 — 남성과 여성용이 구분되어 있어 맞춤 건강 관리가 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 특유의 쓴 맛이 없어 복용하기 부담 없음</t>
+          <t>부담 없는 복용감 — 특유의 쓴맛이 적고 진득해 목넘김과 섭취가 편리함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 — 직장인 체력 충전에 유용하며 복용 후 기운이 잘 남</t>
+          <t>체력 및 활력 증진 — 직장인 체력 보충 및 피로 완화에 효과적인 선물로 평가됨</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3088,24 +3076,28 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>즉각적인 피로 회복 — 복용 후 활력이 생기고 피로가 빠르게 회복됨</t>
+          <t>즉각적인 활력 체감 — 복용 후 피로 회복과 기운 보충이 빠르게 체감됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>깔끔한 선물용 패키지 — 각 잡힌 상자 포장으로 선물하기에 만족스러움</t>
+          <t>넉넉한 용량과 구성 — 타사 에너지 샷 제품 대비 용량이 넉넉해 만족스러움</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>간편한 액상형 섭취 — 액상형이라 마시기 편하며 맛도 좋음</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>고급스러운 선물 박스 — 각 잡힌 깔끔한 단독 패키징으로 선물 가치가 높음</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>음용 시 목메임 — 농도가 진해 섭취 후 목이 메여 물을 추가로 마셔야 할 수 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3147,28 +3139,24 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>29832</v>
+        <v>29834</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간편하고 편한 섭취 — 액상과 알약을 함께 먹기 쉽고 맛도 맛있음</t>
+          <t>목넘김 편한 정제 크기 — 정제 크기가 두껍지 않고 적당해 삼키기 수월함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>생기 및 체력 충전 — 복용 시 아침 피로가 가셔지고 몸에 생기가 살아남</t>
+          <t>풍성한 증정 젤리 구성 — 본품 외에 비타민 젤리가 함께 제공되어 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>맛있는 증정 젤리 — 함께 제공되는 사은품 비타민 젤리의 맛과 구성이 우수함</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>알약 크기의 부담 — 포함된 흰색 알약의 크기가 다소 큰 편임</t>
-        </is>
-      </c>
+          <t>휴대성 및 피로 개선 — 외출이나 여행 시 휴대가 간편하며 아침 피로 개선에 도움 됨</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3210,21 +3198,21 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>풍성한 사은품 구성 — 포토카드 등 추가 증정품 구성이 매우 알참</t>
+          <t>맛있는 복용감 — 베리말차 등 다양한 맛이 있어 거부감 없이 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>부담 없는 기분 좋은 맛 — 맛이 좋아 거부감 없이 맛있게 먹을 수 있음</t>
+          <t>배변 활동 원활 — 꾸준히 섭취 시 화장실을 편하게 가는 데 도움이 됨</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>소화 및 배변 도움 — 섭취 후 속이 편안해지고 화장실을 잘 가게 됨</t>
+          <t>만족스러운 포토카드 사은품 — 아이돌 포토카드 등 사은품 구성이 푸짐해 소장 만족도가 높음</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -3269,26 +3257,26 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>화려하고 고급진 포장 — 패키지와 가방 구성이 예쁘고 고급스러워 개봉 시 감동을 줌</t>
+          <t>고급스러운 선물 패키지 — 오간자 및 플리츠백 구성으로 언박싱 시 높은 만족감을 줌</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>맛있고 쉬운 복용 — 맛이 매우 좋으며 하루 한 병씩 챙겨 마시기 편함</t>
+          <t>피로 완화 및 탄력 기대감 — 섭취 후 피로가 덜하고 피부 건강 관리에 기대감이 높음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>피로감 완화 효과 — 꾸준히 섭취 시 피로한 느낌이 덜해짐</t>
+          <t>맛있고 간편한 앰플형 — 하루 한 병씩 맛있고 간편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>높은 가격대 부담 — 기본 가격대가 있어 할인할 때만 구매하게 됨</t>
+          <t>다소 부담스러운 가격 — 정가 기준 가격대가 높아 할인 시기에 구매를 선호함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3336,27 +3324,31 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 복용 시 속 더부룩함이 사라지고 소화에 도움을 줌</t>
+          <t>속 편한 소화 개선 — 섭취 후 속 더부룩함이 줄고 소화가 잘되는 느낌을 받음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>풍성한 추가 증정 — 단백질바 및 추가 효소 등 감동적인 사은품을 제공함</t>
+          <t>푸짐한 사은품 증정 — 단백질바 및 파인애플 효소 등 사은품이 동봉되어 만족도가 높음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>고급 포장과 가성비 — 포장이 고급스럽고 세일이나 쿠폰 적용 시 가격이 저렴함</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>고급스러운 선물 포장 — 포장이 정갈하여 나를 위한 선물이나 타인 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>지속 구매 시 가격 부담 — 상시 구매하기에 정가 부담이 있어 추가 할인 혜택을 희망함</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3364,58 +3356,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 풍부한 맛 — 퍽퍽하지 않고 촉촉하며 다양한 양념 맛이 매력적임</t>
+          <t>확실한 다음 날 숙취 완화 — 음주 전후 섭취 시 다음 날 아침 두통과 늘어지는 느낌이 덜함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>초간단 조리 방식 — 전자레인지에 데우기만 하면 되어 식사 대용으로 편함</t>
+          <t>고급스러운 쇼핑백 패키징 — 리본 손잡이가 달린 전용 세트 구성으로 선물용 품격이 높음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 할인 행사를 활용하면 싸게 쟁여두기 좋음</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>간편한 개별 스틱 파우치 — 소용량 스틱형 액상이라 모임 자리나 가방에 휴대하여 바로 복용 가능함</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>호불호 있는 한약재 맛 — 쌍화탕이나 한약에 가까운 짙은 맛으로 인해 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3423,62 +3419,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>1913</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 — 음주 전후 복용 시 다음 날 아침 숙취와 무거운 느낌이 확연히 덜함</t>
+          <t>우수한 분말 용해도 — 입자가 곱고 뭉침 없이 부드럽게 잘 녹아 음료에 섞기 편함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 편의성 — 작은 개별 스틱 타입으로 물 없이 장소에 상관없이 먹기 좋음</t>
+          <t>운동 수행 능력 향상 — 꾸준히 복용 시 운동할 때 덜 지치고 세트 수행 횟수가 늘어남</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>고급스러운 선물 패키지 — 보라색 박스와 리본 쇼핑백 포장이 선물용으로 훌륭함</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>한약/쌍화탕 맛 호불호 — 약재 느낌의 진한 쓴맛이 있어 개인차가 존재함</t>
-        </is>
-      </c>
+          <t>스쿱 내장형 편의성 — 적당한 통 크기에 전용 계량 스쿱이 들어있어 섭취가 편리함</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3486,7 +3478,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3496,38 +3488,38 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1913</v>
+        <v>1183</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>부드러운 입자 및 풀림 — 입자가 뭉침 없이 잘 녹아 타 음료나 보충제에 섞기 편함</t>
+          <t>맛있는 매실향 음료감 — 매실 맛으로 거부감 없이 맛있게 물 대신 마실 수 있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 지속 복용 시 운동할 때 지치지 않고 수행 개수가 늘어남</t>
+          <t>찬물에도 잘 풀리는 분말 — 가루 풀림이 좋아 흔들어 타 마시기 편리함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>편리한 계량 수저 — 통 안에 스쿱이 동봉되어 섭취 시 용량 조절이 쉬움</t>
+          <t>운동 중 수분 및 활력 보충 — 운동 중 전해질 및 아미노산 보충으로 수행 능력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3537,7 +3529,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3545,12 +3537,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3560,36 +3552,40 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1183</v>
+        <v>1535</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>맛있는 맛과 향 — 매실 맛 등 향과 맛이 훌륭해 물 대신 마시기 부담 없음</t>
+          <t>아르기닌·밀크씨슬 알찬 조합 — 활력과 간 건강을 동시에 챙길 수 있는 복합 세트 구성임</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>물에 잘 녹는 찬 가루 — 가루가 수월하게 풀려 운동 중 수분 보충용으로 편리함</t>
+          <t>아침 피로 감소 체감 — 섭취 후 아침 기상이 가벼워지고 운동 시 컨디션 관리에 도움 됨</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>체력 및 수행력 유지 — 복용 시 수분과 전해질이 보충되어 운동 차이가 크게 느껴짐</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>2개월분 넉넉한 용량 — 용량이 충분하여 장기간 여유 있게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>쇼핑백 마감 불량 — 동봉된 선물용 쇼핑백에 끈이 누락되어 배송된 사례가 있음</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3604,55 +3600,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1535</v>
+        <v>68</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>실속 있는 영양 조합 — 아르기닌과 밀크씨슬 구성으로 활력과 간 건강을 동시에 케어함</t>
+          <t>촉촉하고 부드러운 육질 — 퍽퍽하지 않고 촉촉하여 식감이 우수함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>피로 완화 체감 — 아침 기상 시 몸이 가볍고 운동이나 일상 피로가 줄어듦</t>
+          <t>질리지 않는 다양한 맛 — 떡볶이맛 등 다채로운 맛 구성으로 물리지 않고 식단 관리 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>쇼핑백 포함 구성 — 선물용 쇼핑백이 함께 증정되어 전달하기 깔끔함</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>쇼핑백 부속 누락 — 증정된 쇼핑백의 끈이 달려있지 않은 채 배송됨</t>
-        </is>
-      </c>
+          <t>간편한 전자레인지 조리 — 해동 및 전자레인지 조리가 간단해 기숙사나 일상에서 먹기 편함</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -3698,17 +3690,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>비린 맛 없는 음료 맛 — 단백질 특유의 텁텁함과 비린 맛이 없고 달콤한 음료 같음</t>
+          <t>비리지 않고 달콤한 맛 — 프로틴 특유의 텁텁함과 비린 맛 없이 일반 초코·모카 음료처럼 맛있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>포만감 및 간식 대용 — 마시고 나면 배가 고프지 않아 단 것이 땡길 때 적합함</t>
+          <t>높은 포만감 제공 — 섭취 후 든든함이 있어 운동 후나 간식 대용으로 적합함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>빠른 득근 수분 섭취 — 운동 직후 간편하게 챙겨 마시기 유용함</t>
+          <t>휴대 편한 팩 음료 — 한 팩씩 가볍게 들고 다니며 즉시 섭취할 수 있음</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3757,22 +3749,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>더부룩함 없는 소화 — 복용 시 속 더부룩함이 없어지고 편안하게 소화됨</t>
+          <t>편안한 소화 및 더부룩함 완화 — 섭취 후 소화가 원활해지고 속이 편안해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>달콤한 콘스프 맛 — 초당옥수수맛으로 콘스프처럼 달콤하여 맛있게 먹을 수 있음</t>
+          <t>달달한 콘스프 맛 — 초당옥수수 콘스프 맛으로 부담 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>넉넉한 용량 및 사은품 — 할인가 대비 사은품과 증정 포수가 풍성함</t>
+          <t>풍성한 100포 대용량 구성 — 증정품과 칩이 포함되어 3개월간 넉넉하게 섭취 가능함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>미세한 맛의 변동 — 이전에 구매해 먹던 맛과 살짝 다름</t>
+          <t>이전 대비 맛 차이 — 기존 제품 대비 미세한 맛의 차이가 느껴진다는 의견 있음</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -4096,7 +4088,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16251</v>
+        <v>16252</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15579</v>
@@ -4111,7 +4103,7 @@
         <v>823</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8747</v>
+        <v>8748</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>816</v>
@@ -4120,10 +4112,10 @@
         <v>783</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>29832</v>
+        <v>29834</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4134,76 +4126,74 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 복용 후 피곤함이 덜 느껴지고 활력에 도움이 됨
-고급스러운 포장 구성 — 구성 및 디자인이 깔끔하고 고급스러워 선물용으로 적합함
-간편한 섭취 방식 — 맛이 좋고 간편하게 챙겨 먹기 편리함</t>
+          <t>피로 회복 체감 — 섭취 후 피로감이 덜해지고 활력 충전에 도움 됨
+선물용 패키지 만족 — 포장이 깔끔하고 튼튼하며 디자인이 고급스러워 선물용으로 적합함
+간편한 섭취 — 액상과 정제 구성으로 어디서나 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>기력 충전 도움 — 피곤하거나 지칠 때 먹으면 기운을 차리는 데 효과적임
-선물용 만족도 — 배송 포장이 예쁘게 와서 주는 사람과 받는 사람 모두 만족함
-편리한 복용 — 환절기 건강 관리 및 피로 시 챙겨 마시기 편함</t>
+          <t>피로 시 간편한 활력 충전 — 지치거나 피곤할 때 하나씩 간편하게 챙겨 먹기 좋음
+선물용 디자인 만족 — 패키지가 깔끔하고 예뻐 선물용 및 수령용 모두 만족도가 높음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 — 복용 시 몸의 활력이 달라지고 다음 날 피로가 확실히 줄어듦
-꼼꼼한 배송 포장 — 포장이 꼼꼼하게 되어 배송 상태가 양호함
-우수한 액상 농도 — 타 액상 비타민 대비 액상이 진하고 품질이 뛰어남</t>
+          <t>뚜렷한 피로 회복 체감 — 복용 후 다음 날 피로가 덜하고 몸에 활력이 생기는 체감 효과가 있음
+진한 액상 맛과 퀄리티 — 타 액상 비타민 대비 맛이 진하고 고품질로 느껴짐
+꼼꼼한 선물 포장 — 포장이 정성스럽고 꼼꼼하여 선물로 주고받기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 새콤달콤한 젤리 형태로 간식처럼 맛있게 섭취 가능함
-쉬운 영양제 섭취 — 알약을 잘 못 먹는 사람도 부담 없이 챙겨 먹기 편함
-귀여운 패키지 디자인 — 패키지 형태와 증정품 키캡 디자인이 귀여움</t>
+          <t>맛있는 구미 형태 — 새콤달콤한 젤리 형태로 간식처럼 거부감 없이 맛있게 먹을 수 있음
+편리한 복용 편의성 — 알약을 잘 삼키지 못하는 사람도 부담 없이 영양을 챙길 수 있음
+귀여운 선물 패키지 — 손잡이가 달린 귀여운 디자인과 꼼꼼한 포장으로 선물 만족도가 높음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 며칠만 복용해도 오후 시간대 체력 저하와 피로감이 줄어듦
-뛰어난 휴대성 — 개별 포장이 견고하여 출근이나 여행 시 가방에 넣기 편리함
-편리한 섭취 방식 — 물 없이도 간편하게 먹을 수 있고 목넘김이 양호함</t>
+          <t>빠른 피로 개선 체감 — 섭취 후 오후 피로감이나 체력 저하가 줄어들고 에너지 충전에 도움 됨
+간편한 휴대 및 섭취 — 물 없이도 개별 포장 병 형태로 출근길이나 야외에서 간편 복용 가능함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>편리한 개별 휴대 — 소포장 한 포씩 외출 시 가방에 넣어 다니며 챙기기 좋음
-아침 피로 감소 — 자기 전 복용 시 아침 피로 회복에 도움이 됨
-고급스러운 구성 — 알약과 음료 세트 구성으로 고급스러운 느낌을 줌</t>
+          <t>간편한 일체형 복용 — 알약과 음료가 세트로 구성되어 휴대 및 섭취가 간편함
+아침 피로 완화 — 취침 전이나 피곤할 때 섭취 시 다음 날 아침 컨디션 회복에 도움 됨
+고급스러운 포장 — 포장이 깔끔하고 고급스러워 가벼운 선물용으로 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 박스와 종이가방 포장이 예쁘고 고급스러워 명절 선물에 적합함
-출근 시 간편 섭취 — 한 병씩 개별 구성되어 있어 출근할 때 챙겨 먹기 편리함
-면역 및 활력 유지 — 체력이 떨어지는 시기나 환절기에 면역력 유지에 도움됨</t>
+          <t>고급스러운 명절 패키지 — 전용 박스와 종이가방 구성이 고급스러워 명절 선물로 적합함
+출근 시 간편한 복용 — 1병 단위 개별 포장이라 출근길에 챙겨 먹기 수월함
+활력 충전 효과 — 바쁜 일상이나 환절기 면역 및 체력 보충에 도움 됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성과 여성을 위한 맞춤 비타민으로 구분되어 선물용으로 좋음
-거부감 없는 맛 — 특유의 쓴 맛이 없어 복용하기 부담 없음
-우수한 피로 회복 — 직장인 체력 충전에 유용하며 복용 후 기운이 잘 남</t>
+          <t>성별 맞춤형 설계 — 남성과 여성용이 구분되어 있어 맞춤 건강 관리가 가능함
+부담 없는 복용감 — 특유의 쓴맛이 적고 진득해 목넘김과 섭취가 편리함
+체력 및 활력 증진 — 직장인 체력 보충 및 피로 완화에 효과적인 선물로 평가됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>즉각적인 피로 회복 — 복용 후 활력이 생기고 피로가 빠르게 회복됨
-깔끔한 선물용 패키지 — 각 잡힌 상자 포장으로 선물하기에 만족스러움
-간편한 액상형 섭취 — 액상형이라 마시기 편하며 맛도 좋음</t>
+          <t>즉각적인 활력 체감 — 복용 후 피로 회복과 기운 보충이 빠르게 체감됨
+넉넉한 용량과 구성 — 타사 에너지 샷 제품 대비 용량이 넉넉해 만족스러움
+고급스러운 선물 박스 — 각 잡힌 깔끔한 단독 패키징으로 선물 가치가 높음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간편하고 편한 섭취 — 액상과 알약을 함께 먹기 쉽고 맛도 맛있음
-생기 및 체력 충전 — 복용 시 아침 피로가 가셔지고 몸에 생기가 살아남
-맛있는 증정 젤리 — 함께 제공되는 사은품 비타민 젤리의 맛과 구성이 우수함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>목넘김 편한 정제 크기 — 정제 크기가 두껍지 않고 적당해 삼키기 수월함
+풍성한 증정 젤리 구성 — 본품 외에 비타민 젤리가 함께 제공되어 맛있게 섭취 가능함
+휴대성 및 피로 개선 — 외출이나 여행 시 휴대가 간편하며 아침 피로 개선에 도움 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4211,35 +4201,34 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송이 매우 느려 받기까지 오랜 시간이 걸림
-압도적 우위 부족 — 가격 대비 타 건강기능식품 대비 확실한 차별성은 애매함</t>
+          <t>대체재 대비 특장점 모호 — 시중 건강기능식품 선택지가 다양해 압도적인 차별성이 부족하다는 의견 있음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>심각한 배송 지연 — 배송이 매우 늦어져 구매 과정에서 불편함을 겪음</t>
+          <t>배송 지연 불만 — 배송이 심하게 지연되어 수령 시 불편을 겪었다는 의견 있음</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 배송 포장 — 선물용 쇼핑백이나 포장 신경 씀 없이 박스에 그대로 배송됨</t>
+          <t>배송 포장 아쉬움 — 쇼핑백 미동봉 및 일반 박스 배송으로 선물용 포장에 아쉬움이 있음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>풍성함 부족한 부피 — 소포장이라 풍성해 보이는 선물 느낌은 약간 부족함</t>
+          <t>다소 작은 소포장 볼륨 — 소포장 구성이라 선물로서 풍성해 보이지 않을 수 있음</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기의 부담 — 포함된 흰색 알약의 크기가 다소 큰 편임</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>음용 시 목메임 — 농도가 진해 섭취 후 목이 메여 물을 추가로 마셔야 할 수 있음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4452,22 +4441,22 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -4509,27 +4498,27 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -4566,27 +4555,27 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -4644,28 +4633,28 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1695</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1913</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1183</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>1535</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>68</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>1913</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>1183</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>1535</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>218</v>
@@ -4682,72 +4671,72 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>풍성한 사은품 구성 — 포토카드 등 추가 증정품 구성이 매우 알참
-부담 없는 기분 좋은 맛 — 맛이 좋아 거부감 없이 맛있게 먹을 수 있음
-소화 및 배변 도움 — 섭취 후 속이 편안해지고 화장실을 잘 가게 됨</t>
+          <t>맛있는 복용감 — 베리말차 등 다양한 맛이 있어 거부감 없이 맛있게 섭취 가능함
+배변 활동 원활 — 꾸준히 섭취 시 화장실을 편하게 가는 데 도움이 됨
+만족스러운 포토카드 사은품 — 아이돌 포토카드 등 사은품 구성이 푸짐해 소장 만족도가 높음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>화려하고 고급진 포장 — 패키지와 가방 구성이 예쁘고 고급스러워 개봉 시 감동을 줌
-맛있고 쉬운 복용 — 맛이 매우 좋으며 하루 한 병씩 챙겨 마시기 편함
-피로감 완화 효과 — 꾸준히 섭취 시 피로한 느낌이 덜해짐</t>
+          <t>고급스러운 선물 패키지 — 오간자 및 플리츠백 구성으로 언박싱 시 높은 만족감을 줌
+피로 완화 및 탄력 기대감 — 섭취 후 피로가 덜하고 피부 건강 관리에 기대감이 높음
+맛있고 간편한 앰플형 — 하루 한 병씩 맛있고 간편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 복용 시 속 더부룩함이 사라지고 소화에 도움을 줌
-풍성한 추가 증정 — 단백질바 및 추가 효소 등 감동적인 사은품을 제공함
-고급 포장과 가성비 — 포장이 고급스럽고 세일이나 쿠폰 적용 시 가격이 저렴함</t>
+          <t>속 편한 소화 개선 — 섭취 후 속 더부룩함이 줄고 소화가 잘되는 느낌을 받음
+푸짐한 사은품 증정 — 단백질바 및 파인애플 효소 등 사은품이 동봉되어 만족도가 높음
+고급스러운 선물 포장 — 포장이 정갈하여 나를 위한 선물이나 타인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 풍부한 맛 — 퍽퍽하지 않고 촉촉하며 다양한 양념 맛이 매력적임
-초간단 조리 방식 — 전자레인지에 데우기만 하면 되어 식사 대용으로 편함
-저렴한 가성비 — 할인 행사를 활용하면 싸게 쟁여두기 좋음</t>
+          <t>확실한 다음 날 숙취 완화 — 음주 전후 섭취 시 다음 날 아침 두통과 늘어지는 느낌이 덜함
+고급스러운 쇼핑백 패키징 — 리본 손잡이가 달린 전용 세트 구성으로 선물용 품격이 높음
+간편한 개별 스틱 파우치 — 소용량 스틱형 액상이라 모임 자리나 가방에 휴대하여 바로 복용 가능함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 — 음주 전후 복용 시 다음 날 아침 숙취와 무거운 느낌이 확연히 덜함
-우수한 휴대성과 편의성 — 작은 개별 스틱 타입으로 물 없이 장소에 상관없이 먹기 좋음
-고급스러운 선물 패키지 — 보라색 박스와 리본 쇼핑백 포장이 선물용으로 훌륭함</t>
+          <t>우수한 분말 용해도 — 입자가 곱고 뭉침 없이 부드럽게 잘 녹아 음료에 섞기 편함
+운동 수행 능력 향상 — 꾸준히 복용 시 운동할 때 덜 지치고 세트 수행 횟수가 늘어남
+스쿱 내장형 편의성 — 적당한 통 크기에 전용 계량 스쿱이 들어있어 섭취가 편리함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 입자 및 풀림 — 입자가 뭉침 없이 잘 녹아 타 음료나 보충제에 섞기 편함
-운동 수행 능력 향상 — 지속 복용 시 운동할 때 지치지 않고 수행 개수가 늘어남
-편리한 계량 수저 — 통 안에 스쿱이 동봉되어 섭취 시 용량 조절이 쉬움</t>
+          <t>맛있는 매실향 음료감 — 매실 맛으로 거부감 없이 맛있게 물 대신 마실 수 있음
+찬물에도 잘 풀리는 분말 — 가루 풀림이 좋아 흔들어 타 마시기 편리함
+운동 중 수분 및 활력 보충 — 운동 중 전해질 및 아미노산 보충으로 수행 능력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 맛과 향 — 매실 맛 등 향과 맛이 훌륭해 물 대신 마시기 부담 없음
-물에 잘 녹는 찬 가루 — 가루가 수월하게 풀려 운동 중 수분 보충용으로 편리함
-체력 및 수행력 유지 — 복용 시 수분과 전해질이 보충되어 운동 차이가 크게 느껴짐</t>
+          <t>아르기닌·밀크씨슬 알찬 조합 — 활력과 간 건강을 동시에 챙길 수 있는 복합 세트 구성임
+아침 피로 감소 체감 — 섭취 후 아침 기상이 가벼워지고 운동 시 컨디션 관리에 도움 됨
+2개월분 넉넉한 용량 — 용량이 충분하여 장기간 여유 있게 복용 가능함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>실속 있는 영양 조합 — 아르기닌과 밀크씨슬 구성으로 활력과 간 건강을 동시에 케어함
-피로 완화 체감 — 아침 기상 시 몸이 가볍고 운동이나 일상 피로가 줄어듦
-쇼핑백 포함 구성 — 선물용 쇼핑백이 함께 증정되어 전달하기 깔끔함</t>
+          <t>촉촉하고 부드러운 육질 — 퍽퍽하지 않고 촉촉하여 식감이 우수함
+질리지 않는 다양한 맛 — 떡볶이맛 등 다채로운 맛 구성으로 물리지 않고 식단 관리 가능함
+간편한 전자레인지 조리 — 해동 및 전자레인지 조리가 간단해 기숙사나 일상에서 먹기 편함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 음료 맛 — 단백질 특유의 텁텁함과 비린 맛이 없고 달콤한 음료 같음
-포만감 및 간식 대용 — 마시고 나면 배가 고프지 않아 단 것이 땡길 때 적합함
-빠른 득근 수분 섭취 — 운동 직후 간편하게 챙겨 마시기 유용함</t>
+          <t>비리지 않고 달콤한 맛 — 프로틴 특유의 텁텁함과 비린 맛 없이 일반 초코·모카 음료처럼 맛있음
+높은 포만감 제공 — 섭취 후 든든함이 있어 운동 후나 간식 대용으로 적합함
+휴대 편한 팩 음료 — 한 팩씩 가볍게 들고 다니며 즉시 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 없는 소화 — 복용 시 속 더부룩함이 없어지고 편안하게 소화됨
-달콤한 콘스프 맛 — 초당옥수수맛으로 콘스프처럼 달콤하여 맛있게 먹을 수 있음
-넉넉한 용량 및 사은품 — 할인가 대비 사은품과 증정 포수가 풍성함</t>
+          <t>편안한 소화 및 더부룩함 완화 — 섭취 후 소화가 원활해지고 속이 편안해지는 느낌을 받음
+달달한 콘스프 맛 — 초당옥수수 콘스프 맛으로 부담 없이 맛있게 먹을 수 있음
+풍성한 100포 대용량 구성 — 증정품과 칩이 포함되어 3개월간 넉넉하게 섭취 가능함</t>
         </is>
       </c>
     </row>
@@ -4760,27 +4749,31 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>높은 가격대 부담 — 기본 가격대가 있어 할인할 때만 구매하게 됨</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>한약/쌍화탕 맛 호불호 — 약재 느낌의 진한 쓴맛이 있어 개인차가 존재함</t>
-        </is>
-      </c>
+          <t>다소 부담스러운 가격 — 정가 기준 가격대가 높아 할인 시기에 구매를 선호함</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>지속 구매 시 가격 부담 — 상시 구매하기에 정가 부담이 있어 추가 할인 혜택을 희망함</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>호불호 있는 한약재 맛 — 쌍화탕이나 한약에 가까운 짙은 맛으로 인해 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 부속 누락 — 증정된 쇼핑백의 끈이 달려있지 않은 채 배송됨</t>
-        </is>
-      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>쇼핑백 마감 불량 — 동봉된 선물용 쇼핑백에 끈이 누락되어 배송된 사례가 있음</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>미세한 맛의 변동 — 이전에 구매해 먹던 맛과 살짝 다름</t>
+          <t>이전 대비 맛 차이 — 기존 제품 대비 미세한 맛의 차이가 느껴진다는 의견 있음</t>
         </is>
       </c>
     </row>
@@ -4807,27 +4800,27 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
           <t>64,200원</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -5027,7 +5020,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5035,12 +5028,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 당케어</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5050,35 +5043,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580761&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250610/qUVshiLfS5KUSiQ9T3cu591580761_00_05qUVshiLfS5KUSiQ9T3cu.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>824</v>
+        <v>7189</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>혈당 및 유산균 케어 — 유산균과 혈당 관리를 동시에 할 수 있음</t>
+          <t>뛰어난 가성비 — 유명 제약사 성분 제품을 합리적이고 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>뛰어난 가격 경쟁력 — 저렴한 가격에 부담 없이 구매 가능함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>물 없이 편한 섭취 — 개별 포장이라 휴대하기 좋고 물 없이 섭취 가능함</t>
-        </is>
-      </c>
+          <t>부담 없는 데일리 관리 — 혈관 건강 및 기초 건강 예방 차원에서 매일 챙기기 용이함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -5086,7 +5075,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5094,53 +5083,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>852</v>
+        <v>3857</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간편한 휴대와 복용 — 휴대가 용이하고 간단히 먹기 편함</t>
+          <t>저렴한 유지 비용 — 가성비가 뛰어나 부담 없이 장기 복용하기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>고용량의 활력 효과 — 고용량 제품으로 복용 시 체감되는 효과가 큼</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>운동용에 적합한 맛 — 맛과 성분이 만족스러워 운동할 때 먹기 좋음</t>
-        </is>
-      </c>
+          <t>과식 후 부담 완화 — 기름진 음식이나 과식 후 간편하게 챙겨 먹기 적합함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>낮은 효과 체감 — 함량이 적어 단기 섭취로는 큰 효과를 느끼기 어려움</t>
+          <t>체중 감량 체감 미미 — 과식 후 섭취 시 뚜렷한 체중 감량 효과는 확인하기 어렵다는 의견 있음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5157,12 +5142,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 숙취해소 노니샷 5포 5회분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5172,32 +5157,36 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000151&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250507/h6NVof0E9taNldehzI8v600000151_00_00h6NVof0E9taNldehzI8v.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>669</v>
+        <v>1431</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>음주 후 숙취 관리 — 술 마신 후 챙겨 먹기 적합한 제품임</t>
+          <t>붓기 완화 체감 — 섭취 시 몸이 덜 붓는 느낌을 받아 꾸준히 복용함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>무난하고 편한 이용 — 애주가들이 소비 니즈에 맞게 무난하게 먹기 좋음</t>
+          <t>음료 대용 수분 보충 — 탄산음료 대신 맛있는 주스처럼 시원하게 마시기 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1회 음용량 대비 아쉬움 — 1포당 물 권장량이 150ml로 적어 금방 마시게 됨</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5212,7 +5201,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5227,39 +5216,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1156</v>
+        <v>1546</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 타사 대비 가격이 저렴하고 가격 대비 효과가 좋음</t>
+          <t>삼키기 편한 미니 캡슐 — 알약 크기가 매우 작아 목넘김이 편하고 아이들도 복용하기 쉬움</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>쉬운 눈 건강 관리 — 알약을 먹기 편해 눈 건강용으로 꾸준히 복용하기 좋음</t>
+          <t>높은 접근성과 가성비 — 저렴한 가격대로 눈 건강 보조제를 꾸준히 챙기기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>단기 복용 시 체감 미비 — 복용 초기에는 뚜렷한 기능 개선 체감이 크지 않다는 의견 있음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5267,47 +5260,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2842</v>
+        <v>1791</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>구수한 커피 대체 맛 — 커피나 맹물 대신 구수하게 마시기 적합함</t>
+          <t>휴대성 높은 소형 캡슐 — 캡슐 크기가 작아 목넘김이 좋고 한 달치 소포장이라 휴대가 용이함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 활용성 — 사용 및 타 마시기 편리한 다이어트 음료임</t>
+          <t>부담 없는 착한 가격 — 가격 대비 장 건강 루틴 유지에 실용적임</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>인기 품목 잦은 품절 — 수요가 높아 매장 및 온라인에서 품절되는 경우가 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5322,12 +5319,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5337,32 +5334,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/RewRRgsZjRVv0Af38IFQ032306204_00_01RewRRgsZjRVv0Af38IFQ.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>550</v>
+        <v>324</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>화장실 이용 도움 — 화장실을 잘 못 갈 때 도움이 되는 제품임</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>소용량 간편 체험 — 12정 소용량으로 다이소에서 부담 없이 입문해보기 좋음</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>신뢰할 수 있는 제약사 제조 — 종근당 브랜드 제품을 합리적으로 간편하게 구매 가능함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>미미한 변비 효과 — 섭취 후 아무런 반응이나 변비 해소 효과를 느끼지 못함</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5377,12 +5374,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5392,43 +5389,43 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>186</v>
+        <v>1137</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>부담 없는 침향 접함 — 저렴한 가격에 침향을 경험할 수 있어 가성비가 좋음</t>
+          <t>여행용 휴대 편의성 — 여행이나 외출 시 소병 형태로 간편하게 챙겨가기 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>활력 및 피로 회복 — 복용 후 피로함이 덜하고 몸에 활력이 생김</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>진하고 깊은 맛 — 하루 한 알 간편하고 깊고 진한 맛을 제공함</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>오일과 레몬의 복합 구성 — 엑스트라버진 올리브유와 레몬즙 조합을 간편하게 섭취함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>강한 신맛 — 레몬 산미가 꽤 강해 섭취 시 많이 시큼하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5436,12 +5433,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5451,33 +5448,33 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000140&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/nz7SB5WS5Csy7uymMIBh600000140_00_00nz7SB5WS5Csy7uymMIBh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1570</v>
+        <v>1667</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>모발 및 손톱 관리 — 머리카락 빠짐이 줄고 튼튼해지는 효과를 봄</t>
+          <t>높은 활용도와 진한 맛 — 원액이 진하여 물이나 올리브유에 타 먹거나 샐러드에 곁들이기 좋음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>적당한 알약 크기 — 알약 크기가 적당하여 섭취 시 목넘김 부담이 없음</t>
+          <t>배변 활동 도움 — 아침 공복에 올리브유와 함께 섭취 시 배변에 도움이 됨</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 가성비가 좋아 자주 재구매하기 좋음</t>
+          <t>스틱형 휴대성 — 개별 포장이라 이동 중이나 여행 시 챙겨 다니기 매우 편리함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -5487,7 +5484,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5495,51 +5492,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2566</v>
+        <v>112</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>달달한 파인애플 맛 — 파인애플 맛이라 맛이 달콤해서 간식용으로 좋음</t>
+          <t>몸이 따뜻해지는 기상 개운함 — 취침 전 복용 시 몸이 따뜻해지고 아침 기상이 개운함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>붓기 완화 도움 — 섭취 시 붓기 완화 효과가 느껴짐</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>높은 당 함량 — 당 수치가 다소 높아 부담이 됨</t>
-        </is>
-      </c>
+          <t>진한 맛과 씹어먹는 편의성 — 맛이 깊고 진하며 하루 한 알 씹어 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>부담 없는 소단량 가성비 — 5천원에 9일분을 가볍게 구매할 수 있어 경제적임</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -5554,48 +5551,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>460</v>
+        <v>187</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>환절기 목 진정 — 기침이나 환절기 목 칼칼함 완화 및 몸을 따뜻하게 해줌</t>
+          <t>피로 회복 및 컨디션 관리 — 섭취 후 몸에 활력이 생기고 피로가 덜한 느낌을 받음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>부담 없는 달콤한 맛 — 너무 쓰지 않고 깔끔하면서 달달한 맛이 남</t>
+          <t>합리적인 침향환 입문 가격 — 고가 제품군인 침향환을 저렴한 가격에 소량 구매할 수 있음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>간편한 스틱 포장 — 스틱 형태로 휴대하기 쉽고 주변에 나눠주기 편리함</t>
+          <t>하루 한 알 간편 섭취 — 휴대와 복용이 간편하여 부모님 선물이나 일상 건강용으로 적합함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -5713,14 +5710,14 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -5733,7 +5730,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5748,12 +5745,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5770,17 +5767,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -5790,32 +5787,32 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>휴럼</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>휴럼</t>
         </is>
       </c>
     </row>
@@ -5827,52 +5824,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 당케어</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 숙취해소 노니샷 5포 5회분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>홀베리 유기농 레몬즙 10포</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>휴럼 하루한알 침향환 9환 9일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
     </row>
@@ -5889,22 +5886,22 @@
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.7</v>
@@ -5920,34 +5917,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>824</v>
+        <v>7189</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>852</v>
+        <v>3857</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>669</v>
+        <v>1431</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1156</v>
+        <v>1546</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2842</v>
+        <v>1791</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>550</v>
+        <v>324</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>186</v>
+        <v>1137</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1570</v>
+        <v>1667</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2566</v>
+        <v>112</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>460</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5958,66 +5955,65 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>혈당 및 유산균 케어 — 유산균과 혈당 관리를 동시에 할 수 있음
-뛰어난 가격 경쟁력 — 저렴한 가격에 부담 없이 구매 가능함
-물 없이 편한 섭취 — 개별 포장이라 휴대하기 좋고 물 없이 섭취 가능함</t>
+          <t>뛰어난 가성비 — 유명 제약사 성분 제품을 합리적이고 저렴한 가격에 구매 가능함
+부담 없는 데일리 관리 — 혈관 건강 및 기초 건강 예방 차원에서 매일 챙기기 용이함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간편한 휴대와 복용 — 휴대가 용이하고 간단히 먹기 편함
-고용량의 활력 효과 — 고용량 제품으로 복용 시 체감되는 효과가 큼
-운동용에 적합한 맛 — 맛과 성분이 만족스러워 운동할 때 먹기 좋음</t>
+          <t>저렴한 유지 비용 — 가성비가 뛰어나 부담 없이 장기 복용하기 좋음
+과식 후 부담 완화 — 기름진 음식이나 과식 후 간편하게 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>음주 후 숙취 관리 — 술 마신 후 챙겨 먹기 적합한 제품임
-무난하고 편한 이용 — 애주가들이 소비 니즈에 맞게 무난하게 먹기 좋음</t>
+          <t>붓기 완화 체감 — 섭취 시 몸이 덜 붓는 느낌을 받아 꾸준히 복용함
+음료 대용 수분 보충 — 탄산음료 대신 맛있는 주스처럼 시원하게 마시기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 타사 대비 가격이 저렴하고 가격 대비 효과가 좋음
-쉬운 눈 건강 관리 — 알약을 먹기 편해 눈 건강용으로 꾸준히 복용하기 좋음</t>
+          <t>삼키기 편한 미니 캡슐 — 알약 크기가 매우 작아 목넘김이 편하고 아이들도 복용하기 쉬움
+높은 접근성과 가성비 — 저렴한 가격대로 눈 건강 보조제를 꾸준히 챙기기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>구수한 커피 대체 맛 — 커피나 맹물 대신 구수하게 마시기 적합함
-간편한 활용성 — 사용 및 타 마시기 편리한 다이어트 음료임</t>
+          <t>휴대성 높은 소형 캡슐 — 캡슐 크기가 작아 목넘김이 좋고 한 달치 소포장이라 휴대가 용이함
+부담 없는 착한 가격 — 가격 대비 장 건강 루틴 유지에 실용적임</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>화장실 이용 도움 — 화장실을 잘 못 갈 때 도움이 되는 제품임</t>
+          <t>소용량 간편 체험 — 12정 소용량으로 다이소에서 부담 없이 입문해보기 좋음
+신뢰할 수 있는 제약사 제조 — 종근당 브랜드 제품을 합리적으로 간편하게 구매 가능함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 침향 접함 — 저렴한 가격에 침향을 경험할 수 있어 가성비가 좋음
-활력 및 피로 회복 — 복용 후 피로함이 덜하고 몸에 활력이 생김
-진하고 깊은 맛 — 하루 한 알 간편하고 깊고 진한 맛을 제공함</t>
+          <t>여행용 휴대 편의성 — 여행이나 외출 시 소병 형태로 간편하게 챙겨가기 좋음
+오일과 레몬의 복합 구성 — 엑스트라버진 올리브유와 레몬즙 조합을 간편하게 섭취함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>모발 및 손톱 관리 — 머리카락 빠짐이 줄고 튼튼해지는 효과를 봄
-적당한 알약 크기 — 알약 크기가 적당하여 섭취 시 목넘김 부담이 없음
-우수한 가성비 — 가성비가 좋아 자주 재구매하기 좋음</t>
+          <t>높은 활용도와 진한 맛 — 원액이 진하여 물이나 올리브유에 타 먹거나 샐러드에 곁들이기 좋음
+배변 활동 도움 — 아침 공복에 올리브유와 함께 섭취 시 배변에 도움이 됨
+스틱형 휴대성 — 개별 포장이라 이동 중이나 여행 시 챙겨 다니기 매우 편리함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>달달한 파인애플 맛 — 파인애플 맛이라 맛이 달콤해서 간식용으로 좋음
-붓기 완화 도움 — 섭취 시 붓기 완화 효과가 느껴짐</t>
+          <t>몸이 따뜻해지는 기상 개운함 — 취침 전 복용 시 몸이 따뜻해지고 아침 기상이 개운함
+진한 맛과 씹어먹는 편의성 — 맛이 깊고 진하며 하루 한 알 씹어 먹기 편함
+부담 없는 소단량 가성비 — 5천원에 9일분을 가볍게 구매할 수 있어 경제적임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>환절기 목 진정 — 기침이나 환절기 목 칼칼함 완화 및 몸을 따뜻하게 해줌
-부담 없는 달콤한 맛 — 너무 쓰지 않고 깔끔하면서 달달한 맛이 남
-간편한 스틱 포장 — 스틱 형태로 휴대하기 쉽고 주변에 나눠주기 편리함</t>
+          <t>피로 회복 및 컨디션 관리 — 섭취 후 몸에 활력이 생기고 피로가 덜한 느낌을 받음
+합리적인 침향환 입문 가격 — 고가 제품군인 침향환을 저렴한 가격에 소량 구매할 수 있음
+하루 한 알 간편 섭취 — 휴대와 복용이 간편하여 부모님 선물이나 일상 건강용으로 적합함</t>
         </is>
       </c>
     </row>
@@ -6030,24 +6026,32 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>낮은 효과 체감 — 함량이 적어 단기 섭취로는 큰 효과를 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>미미한 변비 효과 — 섭취 후 아무런 반응이나 변비 해소 효과를 느끼지 못함</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>체중 감량 체감 미미 — 과식 후 섭취 시 뚜렷한 체중 감량 효과는 확인하기 어렵다는 의견 있음</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1회 음용량 대비 아쉬움 — 1포당 물 권장량이 150ml로 적어 금방 마시게 됨</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>단기 복용 시 체감 미비 — 복용 초기에는 뚜렷한 기능 개선 체감이 크지 않다는 의견 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>인기 품목 잦은 품절 — 수요가 높아 매장 및 온라인에서 품절되는 경우가 있음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛 — 레몬 산미가 꽤 강해 섭취 시 많이 시큼하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>높은 당 함량 — 당 수치가 다소 높아 부담이 됨</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6063,7 +6067,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6078,14 +6082,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
@@ -6098,12 +6102,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6286,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6290,27 +6294,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>26,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492947ko.png?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6325,7 +6329,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6333,27 +6337,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26,000원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492947ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6368,7 +6372,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6376,27 +6380,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6411,7 +6415,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6419,27 +6423,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6462,27 +6466,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6497,7 +6501,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6505,27 +6509,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>24,700원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6540,7 +6544,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6548,50 +6552,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰 바이탈 M/F 멀티비타민&amp;미네랄 30일분 (M:남성,F:여성)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>105,000원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000198827&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019882703ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5041</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>탄산수 활용 에이드 — 꾸덕한 액상을 탄산수에 타서 상큼하게 즐길 수 있음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>확실한 피로 개선 — 피로감을 낮추고 신체 컨디션을 끌어올려 줌</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>물 없는 이중제형 — 액상과 정제로 구성되어 물 없이도 어디서나 먹기 편함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -6607,50 +6595,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>6023</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>빠르고 깊은 숙면 — 잠드는 시간이 단축되고 깊은 잠을 자는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>맛있는 포도 젤리 — 맛있는 포도 맛 젤리 형태로 간식처럼 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>개운한 아침 기상 — 다음 날 머리가 몽롱하지 않고 아침이 개운해짐</t>
-        </is>
-      </c>
+        <v>5564</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6658,7 +6634,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6666,50 +6642,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807374ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>6625</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>식후 체중 관리 — 고칼로리 음식 섭취 후 체지방 감소 케어에 유용함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 굿즈 — 기획 상품으로 증정되는 시나모롤 틴케이스 키링의 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3중 케어 성분 — 카테킨과 비타민 C, D를 함께 챙길 수 있음</t>
-        </is>
-      </c>
+        <v>27113</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6725,51 +6689,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>16267</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748215ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 숙면 도움 — 뒤척임 없이 쉽게 잠들고 푹 잘 수 있게 해줌</t>
+          <t>식후 간편한 다이어트 관리 — 식후 15분 이내에 간편하게 복용하여 체중 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>맛있고 쉬운 젤리 — 맛있는 젤리 형태라 자기 전 부담 없이 챙기기 편리함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>안심 식물성 성분 — 자연 추출 식물성 멜라토닌이라 믿고 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>적당한 캡슐 크기 — 일반 알약 형태로 일상에서 무난하게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>목넘김 시 걸림 현상 — 캡슐 삼킬 때 목 안쪽에 들러붙는 느낌이 있어 약간 불편함</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6884,24 +6844,24 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -6909,14 +6869,14 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -6924,7 +6884,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6941,52 +6901,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
     </row>
@@ -6998,52 +6958,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 바이탈 M/F 멀티비타민&amp;미네랄 30일분 (M:남성,F:여성)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
     </row>
@@ -7059,18 +7019,14 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7084,20 +7040,16 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>5041</v>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>6023</v>
+        <v>5564</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>6625</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>16267</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>27113</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7109,32 +7061,13 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>탄산수 활용 에이드 — 꾸덕한 액상을 탄산수에 타서 상큼하게 즐길 수 있음
-확실한 피로 개선 — 피로감을 낮추고 신체 컨디션을 끌어올려 줌
-물 없는 이중제형 — 액상과 정제로 구성되어 물 없이도 어디서나 먹기 편함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>빠르고 깊은 숙면 — 잠드는 시간이 단축되고 깊은 잠을 자는 데 도움을 줌
-맛있는 포도 젤리 — 맛있는 포도 맛 젤리 형태로 간식처럼 챙겨 먹기 좋음
-개운한 아침 기상 — 다음 날 머리가 몽롱하지 않고 아침이 개운해짐</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>식후 체중 관리 — 고칼로리 음식 섭취 후 체지방 감소 케어에 유용함
-귀여운 산리오 굿즈 — 기획 상품으로 증정되는 시나모롤 틴케이스 키링의 소장 가치가 높음
-3중 케어 성분 — 카테킨과 비타민 C, D를 함께 챙길 수 있음</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 숙면 도움 — 뒤척임 없이 쉽게 잠들고 푹 잘 수 있게 해줌
-맛있고 쉬운 젤리 — 맛있는 젤리 형태라 자기 전 부담 없이 챙기기 편리함
-안심 식물성 성분 — 자연 추출 식물성 멜라토닌이라 믿고 먹을 수 있음</t>
+          <t>식후 간편한 다이어트 관리 — 식후 15분 이내에 간편하게 복용하여 체중 관리에 도움을 줌
+적당한 캡슐 크기 — 일반 알약 형태로 일상에서 무난하게 복용 가능함</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7086,11 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>목넘김 시 걸림 현상 — 캡슐 삼킬 때 목 안쪽에 들러붙는 느낌이 있어 약간 불편함</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7163,52 +7100,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>26,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>26,000원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>24,700원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>31,400원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>105,000원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7338,10 +7275,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -7350,7 +7287,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -7360,10 +7297,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -7372,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7382,25 +7319,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7410,19 +7347,19 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7432,19 +7369,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7466,7 +7403,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7482,6 +7419,28 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
